--- a/output/pdf_financials_xlsx/TORC.xlsx
+++ b/output/pdf_financials_xlsx/TORC.xlsx
@@ -802,7 +802,7 @@
         <v>-0.023371</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.952956</v>
@@ -926,7 +926,7 @@
         <v>-0.023371</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.952956</v>
@@ -1001,7 +1001,7 @@
         <v>-0.023371</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-2.952956</v>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>24.91805</v>
+        <v>-24.91805</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>42.185086</v>
@@ -1103,7 +1103,7 @@
         <v>-0.023371</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.952956</v>
@@ -1153,7 +1153,7 @@
         <v>-0.023371</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.952212</v>
@@ -1215,7 +1215,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2775,16 +2775,16 @@
         <v>0.0339</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.729413</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.46855</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.593967</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.59599</v>
       </c>
     </row>
     <row r="93">
@@ -4600,7 +4600,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -5092,7 +5096,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5512,7 +5520,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -15855,10 +15867,10 @@
         </is>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.498361</v>
+        <v>-0.498361</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2.952956</v>
+        <v>-2.952956</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TORC.xlsx
+++ b/output/pdf_financials_xlsx/TORC.xlsx
@@ -1281,22 +1281,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08254499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.043623</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.01603</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.574735</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.494357</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.030049</v>
       </c>
     </row>
     <row r="35">
@@ -1331,22 +1331,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08254499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.043623</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.01603</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.574735</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.494357</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.030049</v>
       </c>
     </row>
     <row r="37">
@@ -1631,22 +1631,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.094545</v>
+        <v>0.012</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.046952</v>
+        <v>0.003329</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.523592</v>
+        <v>0.507562</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.793269</v>
+        <v>0.218534</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.534011</v>
+        <v>0.039654</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.052413</v>
+        <v>0.022364</v>
       </c>
     </row>
     <row r="49">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/TORC.xlsx
+++ b/output/pdf_financials_xlsx/TORC.xlsx
@@ -577,19 +577,19 @@
         <v>0.015129</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.253472</v>
+        <v>0.254271</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.31641</v>
+        <v>0.45931</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.719571</v>
+        <v>0.934829</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.458199</v>
+        <v>0.679532</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.275298</v>
+        <v>0.333561</v>
       </c>
     </row>
     <row r="8">
@@ -658,13 +658,13 @@
         <v>1.574933</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.719571</v>
+        <v>0.934829</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.458199</v>
+        <v>0.679532</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.275298</v>
+        <v>0.333561</v>
       </c>
     </row>
     <row r="11">
@@ -686,10 +686,10 @@
         <v>-2.784328</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.458199</v>
+        <v>-0.679532</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.275298</v>
+        <v>-0.333561</v>
       </c>
     </row>
     <row r="12">
@@ -808,13 +808,13 @@
         <v>-2.952956</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-2.789863</v>
+        <v>-5.579726</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-2.334</v>
+        <v>-2.27505</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.775514</v>
+        <v>-1.551028</v>
       </c>
     </row>
     <row r="17">
@@ -833,13 +833,13 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>2.789863</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.05895</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>0.775514</v>
       </c>
     </row>
     <row r="18">
@@ -1109,13 +1109,13 @@
         <v>-2.952956</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.789863</v>
+        <v>-5.579726</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.334</v>
+        <v>-2.27505</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.775514</v>
+        <v>-1.551028</v>
       </c>
     </row>
     <row r="28">
@@ -1159,13 +1159,13 @@
         <v>-2.952212</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.786004</v>
+        <v>-5.575867</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.330149</v>
+        <v>-2.271199</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.772338</v>
+        <v>-1.547852</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.591151842816641</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="32">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.079662</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.057503</v>
@@ -3125,7 +3125,7 @@
         <v>0.048094</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.28627</v>
+        <v>-0.365932</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.601711</v>
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.056893</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.039494</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.004736</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.005819</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.05994</v>
       </c>
     </row>
     <row r="111">
@@ -6738,7 +6738,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -9618,7 +9622,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -11496,7 +11504,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -11676,7 +11688,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -12050,7 +12066,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -12694,7 +12714,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -12894,7 +12918,11 @@
           <t>Office expenses 10</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -13362,7 +13390,11 @@
           <t>Loss before income tax recovery</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -13406,7 +13438,11 @@
           <t>Income tax recovery 14</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -13668,7 +13704,11 @@
           <t>Directors’ fees 9</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -13794,7 +13834,11 @@
           <t>Office expenses 9</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -14152,7 +14196,11 @@
           <t>Loss before income tax recovery</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -14196,7 +14244,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -15302,7 +15354,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
